--- a/results/Data S1.xlsx
+++ b/results/Data S1.xlsx
@@ -12224,7 +12224,7 @@
       </c>
       <c r="C11" s="9" t="inlineStr">
         <is>
-          <t>7,432 (7,439 assay records)</t>
+          <t>1,116</t>
         </is>
       </c>
       <c r="D11" s="9" t="inlineStr">
@@ -12260,7 +12260,7 @@
       </c>
       <c r="C12" s="9" t="inlineStr">
         <is>
-          <t>6,309 (6,316 assay records)</t>
+          <t>947</t>
         </is>
       </c>
       <c r="D12" s="9" t="inlineStr">
@@ -12296,7 +12296,7 @@
       </c>
       <c r="C13" s="9" t="inlineStr">
         <is>
-          <t>2,109 / 1,109 / 10,885 / 522</t>
+          <t>317 / 1,109 / 10,885 / 522</t>
         </is>
       </c>
       <c r="D13" s="9" t="inlineStr">
@@ -12322,7 +12322,7 @@
     <row r="14" ht="24" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Note: compound counts are the analysed cohorts, not the full source resources. DILIrank 2.0 contains 1,336 drugs, of which the Task A subset used here is 818. DILIst contains 1,279 records, curated here to 388 small-molecule compounds. The cohort summary is in Table S15; detailed row-level curation records are archived in the GitHub repository (tables_archive/cohort_construction.csv).</t>
+          <t>Note: compound counts are the evaluation cohorts used in this study, not the full source resources. Source sizes are DILIrank 2.0 1,336 drugs (Task A subset 818), DILIst 1,279 records (curated to 388 small-molecule compounds), Tox21 NR-AR 7,432 and NR-ER 6,309 curated compounds, and NASA KC1 2,109 rows (train 1,475, validation 317, test 317). Tox21 counts are per evaluation setting; the scaffold and cluster-out splits evaluate the same compounds under different partitions, so the four-setting totals (4,126 for Tox21, 12,833 for NASA) sum the test sets of the four settings and count each compound twice within an endpoint. The cohort summary is in Supplementary Table S1; detailed row-level curation records are archived in the GitHub repository (tables_archive/cohort_construction.csv).</t>
         </is>
       </c>
       <c r="B14" s="17" t="n"/>
